--- a/testdata/data1.xlsx
+++ b/testdata/data1.xlsx
@@ -1,34 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Playwright\DDT\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Playwright\Playwright-Data-driven-testing\testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A4A550-78E0-4B52-ACE7-5730290C7BBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A7AFC76-12A7-4DF0-AB09-63736B057991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5760" yWindow="3720" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="11">
   <si>
     <t>email</t>
   </si>
@@ -485,4 +483,68 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B6C58F7-286E-4786-82DC-DE238711D9F8}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="29.21875" customWidth="1"/>
+    <col min="2" max="2" width="25.33203125" customWidth="1"/>
+    <col min="3" max="3" width="19.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" xr:uid="{087251C1-C9A1-4635-AE75-E830C21F8CF9}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{C098E330-0F7A-4CEE-B257-7B3E2B703286}"/>
+    <hyperlink ref="A4" r:id="rId3" xr:uid="{FBB764CD-8143-45CE-97F7-5BFE5130F1FC}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>